--- a/custom_env/skill_util/Haoqiang/Points.xlsx
+++ b/custom_env/skill_util/Haoqiang/Points.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB00A15A-A6FD-8D4D-A74F-D688A3A6D181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74560655-AFEC-0B49-A866-CCF9D9DFC122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11940" yWindow="5940" windowWidth="27700" windowHeight="16860" xr2:uid="{713D3B50-49F0-CB4F-B1EC-A0311DEB4DDE}"/>
+    <workbookView xWindow="-30100" yWindow="10360" windowWidth="27300" windowHeight="16360" xr2:uid="{A597AB02-480C-1147-8690-9B54E2A301A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1176,7 +1176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9CD9AF2-EDC4-F546-A257-D5FE4ADE8A84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A39490-F5F3-AB4C-8E75-7C9891EA5E20}">
   <dimension ref="A1:FT5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
